--- a/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
+++ b/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\Govt Staff Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7A3B66-CD7C-4DFF-8B18-446B6D0C62FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067E70C7-3C9A-42EA-9328-B656686C9E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{866F53D6-24F6-4A13-A2A6-480F7704B256}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>S No</t>
   </si>
@@ -226,6 +226,15 @@
   </si>
   <si>
     <t>0336-2078953</t>
+  </si>
+  <si>
+    <t>B.E and B Ed</t>
+  </si>
+  <si>
+    <t>B Ed and B.Com</t>
+  </si>
+  <si>
+    <t>0303-0275939</t>
   </si>
 </sst>
 </file>
@@ -233,7 +242,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="d\-m\-yy"/>
+    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -602,9 +611,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -620,9 +626,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -632,9 +635,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,11 +644,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -659,11 +666,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -678,15 +684,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -694,6 +691,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1022,13 +1031,13 @@
     <col min="4" max="4" width="9.42578125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.140625" customWidth="1"/>
     <col min="9" max="9" width="29.42578125" customWidth="1"/>
     <col min="10" max="10" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>55</v>
       </c>
@@ -1042,100 +1051,100 @@
       <c r="I1" s="19"/>
       <c r="J1" s="20"/>
     </row>
-    <row r="2" spans="1:10" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
-    </row>
-    <row r="3" spans="1:10" s="21" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="25" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="23"/>
+    </row>
+    <row r="3" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:10" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <v>16</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>10058374</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="30">
         <v>64040</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="30">
         <v>35074</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1153,21 +1162,21 @@
       <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="31">
         <v>30015</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="31">
         <v>37246</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1185,21 +1194,21 @@
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="31">
         <v>29221</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="31">
         <v>42100</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1217,21 +1226,21 @@
       <c r="F8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="31">
         <v>26063</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="31">
         <v>33848</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1249,21 +1258,21 @@
       <c r="F9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="31">
         <v>24942</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="31">
         <v>33181</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1281,21 +1290,21 @@
       <c r="F10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="31">
         <v>32201</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="31">
         <v>43899</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1311,17 +1320,21 @@
       <c r="F11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
+      <c r="G11" s="31">
+        <v>33044</v>
+      </c>
+      <c r="H11" s="31">
         <v>45433</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1337,21 +1350,21 @@
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="31">
         <v>32227</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="31">
         <v>45434</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1367,21 +1380,21 @@
       <c r="F13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="31">
         <v>35252</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="31">
         <v>45443</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1399,19 +1412,21 @@
       <c r="F14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="31">
         <v>35278</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="31">
         <v>44837</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="5" t="s">
+      <c r="I14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1429,90 +1444,94 @@
       <c r="F15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="31">
         <v>34700</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="31">
         <v>44721</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="5" t="s">
+      <c r="I15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>18</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>10475117</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="32">
         <v>28311</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="32">
         <v>38244</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="9" t="s">
+      <c r="I16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="33"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="11">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="12">
         <v>1</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="12">
         <v>10304582</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="33">
         <v>26115</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="33">
         <v>40732</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1526,6 +1545,6 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
+++ b/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\Govt Staff Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067E70C7-3C9A-42EA-9328-B656686C9E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C965EC4A-90B4-493E-B3E9-BB51BAF740CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{866F53D6-24F6-4A13-A2A6-480F7704B256}"/>
   </bookViews>
@@ -242,7 +242,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -657,6 +657,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -691,18 +703,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1038,46 +1038,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="23"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="26"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="30"/>
     </row>
     <row r="4" spans="1:10" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
@@ -1130,10 +1130,10 @@
       <c r="F5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="18">
         <v>64040</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="18">
         <v>35074</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -1162,10 +1162,10 @@
       <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="19">
         <v>30015</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="19">
         <v>37246</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1194,10 +1194,10 @@
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="19">
         <v>29221</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="19">
         <v>42100</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -1226,10 +1226,10 @@
       <c r="F8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="19">
         <v>26063</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="19">
         <v>33848</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1258,10 +1258,10 @@
       <c r="F9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="19">
         <v>24942</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="19">
         <v>33181</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1290,10 +1290,10 @@
       <c r="F10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="19">
         <v>32201</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="19">
         <v>43899</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1320,10 +1320,10 @@
       <c r="F11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="19">
         <v>33044</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="19">
         <v>45433</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1350,10 +1350,10 @@
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="19">
         <v>32227</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="19">
         <v>45434</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1380,10 +1380,10 @@
       <c r="F13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="19">
         <v>35252</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="19">
         <v>45443</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1412,10 +1412,10 @@
       <c r="F14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="19">
         <v>35278</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="19">
         <v>44837</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1444,10 +1444,10 @@
       <c r="F15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="19">
         <v>34700</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="19">
         <v>44721</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1476,10 +1476,10 @@
       <c r="F16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="20">
         <v>28311</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="20">
         <v>38244</v>
       </c>
       <c r="I16" s="6" t="s">
@@ -1490,18 +1490,18 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
     </row>
     <row r="18" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
@@ -1522,10 +1522,10 @@
       <c r="F18" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="21">
         <v>26115</v>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="21">
         <v>40732</v>
       </c>
       <c r="I18" s="12" t="s">

--- a/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
+++ b/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\Govt Staff Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C965EC4A-90B4-493E-B3E9-BB51BAF740CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215E846-620C-4083-9174-8AA878576F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{866F53D6-24F6-4A13-A2A6-480F7704B256}"/>
   </bookViews>
@@ -289,13 +289,19 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="24">
     <border>
@@ -608,102 +614,102 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1037,129 +1043,129 @@
     <col min="10" max="10" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="27"/>
-    </row>
-    <row r="3" spans="1:10" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="30"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="14">
         <v>16</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="14">
         <v>10058374</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="15">
         <v>64040</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="15">
         <v>35074</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="17">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="18">
         <v>14</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="18">
         <v>10228963</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="19">
@@ -1168,30 +1174,30 @@
       <c r="H6" s="19">
         <v>37246</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="17">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="18">
         <v>14</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="18">
         <v>10833448</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="19">
@@ -1200,30 +1206,30 @@
       <c r="H7" s="19">
         <v>42100</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="20" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="18">
         <v>16</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="18">
         <v>10083703</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="19">
@@ -1232,30 +1238,30 @@
       <c r="H8" s="19">
         <v>33848</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="20" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="17">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="18">
         <v>16</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="18">
         <v>10409986</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="18" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="19">
@@ -1264,30 +1270,30 @@
       <c r="H9" s="19">
         <v>33181</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="20" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="17">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="18">
         <v>14</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="18">
         <v>10966851</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="18" t="s">
         <v>34</v>
       </c>
       <c r="G10" s="19">
@@ -1296,28 +1302,28 @@
       <c r="H10" s="19">
         <v>43899</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="20" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="17">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="18">
         <v>14</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G11" s="19">
@@ -1326,28 +1332,28 @@
       <c r="H11" s="19">
         <v>45433</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="17">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="18">
         <v>14</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="18"/>
+      <c r="F12" s="18" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="19">
@@ -1356,28 +1362,28 @@
       <c r="H12" s="19">
         <v>45434</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="20" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="17">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="18">
         <v>14</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="18"/>
+      <c r="F13" s="18" t="s">
         <v>43</v>
       </c>
       <c r="G13" s="19">
@@ -1386,30 +1392,30 @@
       <c r="H13" s="19">
         <v>45443</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="17">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="18">
         <v>14</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="18">
         <v>11021020</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="18" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="19">
@@ -1418,30 +1424,30 @@
       <c r="H14" s="19">
         <v>44837</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="A15" s="17">
         <v>11</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="18">
         <v>14</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="18">
         <v>1108342</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="18" t="s">
         <v>50</v>
       </c>
       <c r="G15" s="19">
@@ -1450,88 +1456,88 @@
       <c r="H15" s="19">
         <v>44721</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="A16" s="22">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="23">
         <v>18</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="23">
         <v>10475117</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="24">
         <v>28311</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="24">
         <v>38244</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="33"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+      <c r="A18" s="29">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="30">
         <v>1</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="30">
         <v>10304582</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="31">
         <v>26115</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="31">
         <v>40732</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="32" t="s">
         <v>63</v>
       </c>
     </row>

--- a/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
+++ b/Sindhi Muslim/Staff Record/Govt Staff Record/Staff Bio Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\Govt Staff Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215E846-620C-4083-9174-8AA878576F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E641F1F-0CFE-4E6B-BFFD-E554B805629B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{866F53D6-24F6-4A13-A2A6-480F7704B256}"/>
   </bookViews>
@@ -615,6 +615,66 @@
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -627,6 +687,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -639,54 +702,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -695,21 +710,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1044,500 +1044,500 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="6"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="9"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="30"/>
     </row>
     <row r="4" spans="1:10" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="6">
         <v>16</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="6">
         <v>10058374</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="15">
-        <v>64040</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="G5" s="7">
+        <v>27515</v>
+      </c>
+      <c r="H5" s="7">
         <v>35074</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="10">
         <v>14</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="10">
         <v>10228963</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="11">
         <v>30015</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="11">
         <v>37246</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="10">
         <v>14</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="10">
         <v>10833448</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="11">
         <v>29221</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="11">
         <v>42100</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="10">
         <v>16</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="10">
         <v>10083703</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="11">
         <v>26063</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="11">
         <v>33848</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="10">
         <v>16</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="10">
         <v>10409986</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="11">
         <v>24942</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="11">
         <v>33181</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="10">
         <v>14</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="10">
         <v>10966851</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="11">
         <v>32201</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="11">
         <v>43899</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
+      <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="10">
         <v>14</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18" t="s">
+      <c r="E11" s="10"/>
+      <c r="F11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="11">
         <v>33044</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="11">
         <v>45433</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="12" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="10">
         <v>14</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="11">
         <v>32227</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="11">
         <v>45434</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
+      <c r="A13" s="9">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="10">
         <v>14</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18" t="s">
+      <c r="E13" s="10"/>
+      <c r="F13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="11">
         <v>35252</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="11">
         <v>45443</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="12" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
+      <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="10">
         <v>14</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="10">
         <v>11021020</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="11">
         <v>35278</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="11">
         <v>44837</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
+      <c r="A15" s="9">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="10">
         <v>14</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="10">
         <v>1108342</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="11">
         <v>34700</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="11">
         <v>44721</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22">
+      <c r="A16" s="14">
         <v>12</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="15">
         <v>18</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="15">
         <v>10475117</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="16">
         <v>28311</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="16">
         <v>38244</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="28"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
     </row>
     <row r="18" spans="1:10" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="29">
+      <c r="A18" s="18">
         <v>14</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="19">
         <v>1</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="19">
         <v>10304582</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="20">
         <v>26115</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="20">
         <v>40732</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="I18" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J18" s="32" t="s">
+      <c r="J18" s="21" t="s">
         <v>63</v>
       </c>
     </row>
